--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2015_T3_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2015_T3_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>93</t>
+    <t>89</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -63,16 +63,16 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>0.161</t>
-  </si>
-  <si>
-    <t>(0.038)</t>
-  </si>
-  <si>
-    <t>0.280</t>
-  </si>
-  <si>
-    <t>(0.077)</t>
+    <t>0.169</t>
+  </si>
+  <si>
+    <t>(0.040)</t>
+  </si>
+  <si>
+    <t>0.292</t>
+  </si>
+  <si>
+    <t>(0.080)</t>
   </si>
   <si>
     <t>21</t>
@@ -99,7 +99,7 @@
     <t>.n</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -111,10 +111,10 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.315***</t>
-  </si>
-  <si>
-    <t>0.578***</t>
+    <t>0.308***</t>
+  </si>
+  <si>
+    <t>0.565***</t>
   </si>
 </sst>
 </file>
